--- a/dataPrepare/ICU监测数据集.xlsx
+++ b/dataPrepare/ICU监测数据集.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="508">
   <si>
     <t>I. 基础生命体征（持续/高频监测）</t>
   </si>
@@ -958,6 +958,12 @@
   </si>
   <si>
     <t>肺动脉嵌顿压PAWP</t>
+  </si>
+  <si>
+    <t>PCWP</t>
+  </si>
+  <si>
+    <t>5-15</t>
   </si>
   <si>
     <t>&lt;800</t>
@@ -2182,18 +2188,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF404040"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <vertAlign val="subscript"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF404040"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
@@ -2794,7 +2800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2817,6 +2823,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
@@ -3175,13 +3184,13 @@
     <xdr:from>
       <xdr:col>34</xdr:col>
       <xdr:colOff>217170</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>31115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>61595</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>38735</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3199,7 +3208,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="44557950" y="7447915"/>
+          <a:off x="44557950" y="7828915"/>
           <a:ext cx="8652510" cy="2674620"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3474,1227 +3483,1227 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:6">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" hidden="1" spans="1:6">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:6">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="17"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="18" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:6">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:6">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1" spans="1:6">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="18" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:6">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="20" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:5">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="17" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1" spans="1:5">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="18" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" ht="43" customHeight="1" spans="1:5">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" ht="31" customHeight="1" spans="1:5">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="18" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:5">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="18" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="23" ht="27" spans="1:5">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" ht="27" spans="1:5">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1" spans="1:5">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
     </row>
     <row r="28" ht="49" customHeight="1" spans="1:5">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:5">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1" spans="1:5">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17" t="s">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="18" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="32" ht="15" spans="1:5">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17" t="s">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="18" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17" t="s">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="34" ht="15" spans="1:5">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17" t="s">
+      <c r="B34" s="18"/>
+      <c r="C34" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="35" ht="27" customHeight="1" spans="1:5">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="18" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="36" ht="29" customHeight="1" spans="1:5">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="18" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="37" ht="27" spans="1:5">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="18" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="38" ht="15" spans="1:5">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="18" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:5">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="18" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="40" ht="27" spans="1:5">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="18" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:5">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="18" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="42" ht="28.5" spans="1:5">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="18" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="43" ht="15" spans="1:5">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="18" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="44" ht="15" spans="1:5">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="18" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="25"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="26"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="28"/>
+      <c r="A47" s="27"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="29"/>
     </row>
     <row r="48" ht="31" customHeight="1" spans="1:5">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="16" t="s">
+      <c r="E48" s="17" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="18" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="30"/>
-      <c r="B50" s="17" t="s">
+      <c r="A50" s="31"/>
+      <c r="B50" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="31"/>
-      <c r="B51" s="17" t="s">
+      <c r="A51" s="32"/>
+      <c r="B51" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="18" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="18" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="30"/>
-      <c r="B53" s="17" t="s">
+      <c r="A53" s="31"/>
+      <c r="B53" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="18" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="31"/>
-      <c r="B54" s="17" t="s">
+      <c r="A54" s="32"/>
+      <c r="B54" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="18" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="55" ht="15" spans="1:5">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="18" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="30"/>
-      <c r="B56" s="17" t="s">
+      <c r="A56" s="31"/>
+      <c r="B56" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="18" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="31"/>
-      <c r="B57" s="17" t="s">
+      <c r="A57" s="32"/>
+      <c r="B57" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="18" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="30"/>
-      <c r="B59" s="17" t="s">
+      <c r="A59" s="31"/>
+      <c r="B59" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="18" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="60" ht="15" spans="1:5">
-      <c r="A60" s="31"/>
-      <c r="B60" s="17" t="s">
+      <c r="A60" s="32"/>
+      <c r="B60" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="18" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="18" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="31"/>
-      <c r="B62" s="17" t="s">
+      <c r="A62" s="32"/>
+      <c r="B62" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="18" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="15"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:4">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D66" s="17" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1" spans="1:4">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="18" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="68" ht="29" customHeight="1" spans="1:4">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="18" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1" spans="1:4">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="18" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1" spans="1:4">
-      <c r="A70" s="31"/>
-      <c r="B70" s="17" t="s">
+      <c r="A70" s="32"/>
+      <c r="B70" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="18" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:4">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="18" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1" spans="1:4">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="18" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="32" t="s">
+      <c r="A74" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
+      <c r="B74" s="33"/>
+      <c r="C74" s="33"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="32"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="33"/>
     </row>
     <row r="76" ht="29" customHeight="1" spans="1:3">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="17" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="29" t="s">
+      <c r="A77" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C77" s="18" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="78" ht="45" customHeight="1" spans="1:3">
-      <c r="A78" s="30"/>
-      <c r="B78" s="17" t="s">
+      <c r="A78" s="31"/>
+      <c r="B78" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="18" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="79" ht="28.5" spans="1:3">
-      <c r="A79" s="31"/>
-      <c r="B79" s="17" t="s">
+      <c r="A79" s="32"/>
+      <c r="B79" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C79" s="18" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B80" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="18" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="81" ht="27" spans="1:3">
-      <c r="A81" s="30"/>
-      <c r="B81" s="17" t="s">
+      <c r="A81" s="31"/>
+      <c r="B81" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="C81" s="17" t="s">
+      <c r="C81" s="18" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="31"/>
-      <c r="B82" s="17" t="s">
+      <c r="A82" s="32"/>
+      <c r="B82" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="18" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="29" t="s">
+      <c r="A83" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="18" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="30"/>
-      <c r="B84" s="17" t="s">
+      <c r="A84" s="31"/>
+      <c r="B84" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C84" s="18" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="85" ht="15" spans="1:3">
-      <c r="A85" s="31"/>
-      <c r="B85" s="17" t="s">
+      <c r="A85" s="32"/>
+      <c r="B85" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="18" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="B87" s="15"/>
-      <c r="C87" s="15"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="15"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
+      <c r="A88" s="16"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
     </row>
     <row r="89" ht="23" customHeight="1" spans="1:3">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="17" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:3">
-      <c r="A90" s="17" t="s">
+      <c r="A90" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B90" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="C90" s="17" t="s">
+      <c r="C90" s="18" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="91" ht="46" customHeight="1" spans="1:3">
-      <c r="A91" s="17" t="s">
+      <c r="A91" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B91" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="C91" s="17" t="s">
+      <c r="C91" s="18" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="92" ht="43" customHeight="1" spans="1:3">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="C92" s="17" t="s">
+      <c r="C92" s="18" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="93" ht="28.5" spans="1:3">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B93" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="18" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="94" ht="37" customHeight="1" spans="1:3">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B94" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="C94" s="17" t="s">
+      <c r="C94" s="18" t="s">
         <v>274</v>
       </c>
     </row>
@@ -4728,7 +4737,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.225" style="1" customWidth="1"/>
@@ -4771,16 +4780,16 @@
       <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="M1" s="12"/>
+      <c r="M1" s="13"/>
     </row>
     <row r="2" customHeight="1" spans="1:13">
       <c r="A2" s="4" t="s">
@@ -4795,10 +4804,10 @@
         <v>280</v>
       </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="15"/>
     </row>
     <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="6" t="s">
@@ -4834,7 +4843,7 @@
       <c r="L3" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="M3" s="14"/>
+      <c r="M3" s="15"/>
     </row>
     <row r="4" customHeight="1" spans="1:13">
       <c r="A4" s="6" t="s">
@@ -4870,7 +4879,7 @@
       <c r="L4" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="M4" s="14"/>
+      <c r="M4" s="15"/>
     </row>
     <row r="5" customHeight="1" spans="1:13">
       <c r="A5" s="6" t="s">
@@ -4903,323 +4912,308 @@
       <c r="L5" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="M5" s="14"/>
+      <c r="M5" s="15"/>
     </row>
     <row r="6" customHeight="1" spans="1:13">
-      <c r="A6" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="H6" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>302</v>
-      </c>
+      <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="M6" s="14"/>
+        <v>299</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="15"/>
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="A7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
+      <c r="A8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D8" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="H9" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="M7" s="14"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="H8" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="M8" s="14"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="M9" s="14"/>
+      <c r="M9" s="15"/>
     </row>
     <row r="10" customHeight="1" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="M10" s="14"/>
+      <c r="M10" s="15"/>
     </row>
     <row r="11" customHeight="1" spans="1:13">
       <c r="A11" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="L11" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
+      <c r="A12" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C12" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>338</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="M11" s="14"/>
-    </row>
-    <row r="12" ht="44" customHeight="1" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" ht="44" customHeight="1" spans="1:13">
+      <c r="A13" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="D13" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="F13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="I13" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="M12" s="14"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="6" t="s">
+      <c r="K13" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="L13" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>357</v>
-      </c>
+      <c r="M13" s="15"/>
     </row>
     <row r="14" customHeight="1" spans="1:12">
       <c r="A14" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="K14" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="L14" s="9" t="s">
         <v>359</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:12">
       <c r="A15" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>118</v>
@@ -5228,33 +5222,33 @@
         <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>369</v>
+      <c r="H15" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:12">
       <c r="A16" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>118</v>
@@ -5263,645 +5257,680 @@
         <v>14</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>375</v>
+      <c r="H16" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:12">
       <c r="A17" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="K17" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="L17" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
+      <c r="A18" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="I17" s="8" t="s">
+      <c r="F18" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="L17" s="8" t="s">
+      <c r="J18" s="9" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:12">
-      <c r="A18" s="5" t="s">
+      <c r="K18" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="H18" s="8" t="s">
+      <c r="L18" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="I18" s="8" t="s">
+    </row>
+    <row r="19" customHeight="1" spans="1:12">
+      <c r="A19" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="H19" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="L18" s="8" t="s">
+      <c r="J19" s="9" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:12">
-      <c r="A19" s="9" t="s">
+      <c r="K19" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:12">
+      <c r="A20" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>394</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:12">
-      <c r="A20" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>399</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:12">
+      <c r="A21" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="E21" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:11">
-      <c r="A21" s="9"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6" t="s">
+      <c r="F21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
+      <c r="A22" s="10"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="9" t="s">
+      <c r="J22" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
+      <c r="A23" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>105</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>287</v>
+        <v>14</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="K23" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
-      <c r="A24" s="9" t="s">
-        <v>420</v>
+      <c r="A24" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>105</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="K24" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="D24" s="6" t="s">
+    </row>
+    <row r="25" customHeight="1" spans="1:11">
+      <c r="A25" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="B25" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="D25" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="E25" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="I25" s="9" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:11">
-      <c r="A25" s="9" t="s">
+      <c r="J25" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:11">
+      <c r="A26" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="B26" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="H25" s="8" t="s">
+      <c r="D26" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="E26" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:11">
-      <c r="A26" s="5" t="s">
+      <c r="I26" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="H26" s="8" t="s">
+      <c r="K26" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8" t="s">
+    </row>
+    <row r="27" customHeight="1" spans="1:11">
+      <c r="A27" s="5" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:9">
-      <c r="A27" s="6" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="H27" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:9">
+      <c r="A28" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="C28" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:11">
-      <c r="A28" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="I28" s="11" t="s">
         <v>443</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
       <c r="A29" s="6" t="s">
-        <v>220</v>
+        <v>444</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="K29" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="E29" s="6" t="s">
+    </row>
+    <row r="30" customHeight="1" spans="1:11">
+      <c r="A30" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="8" t="s">
+      <c r="D30" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="E30" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:11">
-      <c r="A30" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>460</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:11">
+      <c r="A31" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="E31" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="F31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="I31" s="9" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="8:12">
-      <c r="H31" s="10" t="s">
+      <c r="J31" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" customHeight="1" spans="8:11">
-      <c r="H32" s="8" t="s">
+      <c r="K31" s="9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="8:12">
+      <c r="H32" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" customHeight="1" spans="8:11">
+      <c r="H33" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="8:11">
-      <c r="H33" s="8" t="s">
+      <c r="I33" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="9" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="8:11">
+      <c r="H34" s="9" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="8:11">
-      <c r="H34" s="8" t="s">
+      <c r="I34" s="9"/>
+      <c r="J34" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="K34" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="J34" s="8" t="s">
+    </row>
+    <row r="35" customHeight="1" spans="8:11">
+      <c r="H35" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="K34" s="8"/>
-    </row>
-    <row r="35" customHeight="1" spans="8:11">
-      <c r="H35" s="8" t="s">
+      <c r="I35" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8" t="s">
+      <c r="J35" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="K35" s="8"/>
+      <c r="K35" s="9"/>
     </row>
     <row r="36" customHeight="1" spans="8:11">
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="J36" s="8" t="s">
+      <c r="I36" s="9"/>
+      <c r="J36" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="K36" s="8" t="s">
+      <c r="K36" s="9"/>
+    </row>
+    <row r="37" customHeight="1" spans="8:11">
+      <c r="H37" s="9" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="8:11">
-      <c r="H37" s="8" t="s">
+      <c r="I37" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="J37" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8" t="s">
+      <c r="K37" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="K37" s="8" t="s">
+    </row>
+    <row r="38" customHeight="1" spans="8:11">
+      <c r="H38" s="9" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="8:11">
-      <c r="H38" s="8" t="s">
+      <c r="I38" s="9"/>
+      <c r="J38" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8" t="s">
+      <c r="K38" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="K38" s="8"/>
     </row>
     <row r="39" customHeight="1" spans="8:11">
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="9"/>
+      <c r="J39" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="K39" s="9"/>
+    </row>
+    <row r="40" customHeight="1" spans="8:11">
+      <c r="H40" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="K39" s="8"/>
-    </row>
-    <row r="40" customHeight="1" spans="8:11">
-      <c r="H40" s="8" t="s">
+      <c r="I40" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="J40" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="K40" s="9"/>
+    </row>
+    <row r="41" customHeight="1" spans="8:11">
+      <c r="H41" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="K40" s="8"/>
-    </row>
-    <row r="41" customHeight="1" spans="8:11">
-      <c r="H41" s="8" t="s">
+      <c r="I41" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
+      <c r="J41" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="K41" s="9"/>
     </row>
     <row r="42" customHeight="1" spans="8:11">
-      <c r="H42" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8" t="s">
+      <c r="H42" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="K42" s="8" t="s">
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+    </row>
+    <row r="43" customHeight="1" spans="8:11">
+      <c r="H43" s="9" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="8:11">
-      <c r="H43" s="8" t="s">
+      <c r="I43" s="9"/>
+      <c r="J43" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="K43" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="J43" s="8" t="s">
+    </row>
+    <row r="44" customHeight="1" spans="8:11">
+      <c r="H44" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="K43" s="8"/>
-    </row>
-    <row r="44" customHeight="1" spans="8:11">
-      <c r="H44" s="8" t="s">
+      <c r="I44" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="J44" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="J44" s="8" t="s">
+      <c r="K44" s="9"/>
+    </row>
+    <row r="45" customHeight="1" spans="8:11">
+      <c r="H45" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="K44" s="8"/>
-    </row>
-    <row r="45" customHeight="1" spans="8:11">
-      <c r="H45" s="8" t="s">
+      <c r="I45" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="K45" s="8"/>
+      <c r="J45" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" customHeight="1" spans="8:11">
-      <c r="H46" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8" t="s">
+      <c r="H46" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="K46" s="8"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="K46" s="9"/>
     </row>
     <row r="47" customHeight="1" spans="8:11">
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" customHeight="1" spans="8:11">
-      <c r="H48" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8" t="s">
+      <c r="H48" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="K48" s="8"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+    </row>
+    <row r="49" customHeight="1" spans="8:11">
+      <c r="H49" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="K49" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
